--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationdosage.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationdosage.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationdosage.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationdosage.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2740" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2739" uniqueCount="489">
   <si>
     <t>Property</t>
   </si>
@@ -477,17 +477,19 @@
 </t>
   </si>
   <si>
-    <t>投与日時</t>
-  </si>
-  <si>
-    <t>Describes the occurrence of an event that may occur multiple times. Timing schedules are used for specifying when events are expected or requested to occur, and may also be used to represent the summary of a past or ongoing event.  For simplicity, the definitions of Timing components are expressed as 'future' events, but such components can also be used to describe historic or ongoing events.
-A Timing schedule can be a list of events and/or criteria for when the event happens, which can be expressed in a structured form and/or as a code. When both event and a repeating specification are provided, the list of events should be understood as an interpretation of the information in the repeat structure.</t>
+    <t>When medication should be administered</t>
+  </si>
+  <si>
+    <t>When medication should be administered.</t>
+  </si>
+  <si>
+    <t>This attribute might not always be populated while the Dosage.text is expected to be populated.  If both are populated, then the Dosage.text should reflect the content of the Dosage.timing.</t>
   </si>
   <si>
     <t>The timing schedule for giving the medication to the patient. This  data type allows many different expressions. For example: "Every 8 hours"; "Three times a day"; "1/2 an hour before breakfast for 10 days from 23-Dec 2011:"; "15 Oct 2013, 17 Oct 2013 and 1 Nov 2013".  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
   </si>
   <si>
-    <t>QSET&lt;TS&gt; (GTS)</t>
+    <t>.effectiveTime</t>
   </si>
   <si>
     <t>Dosage.timing.id</t>
@@ -1413,18 +1415,7 @@
     <t>The amount of therapeutic or other substance given at one administration event.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>RXO-2, RXE-3</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.rate[x]</t>
@@ -1467,19 +1458,6 @@
 </t>
   </si>
   <si>
-    <t>１日当たりでの薬剤の投入量</t>
-  </si>
-  <si>
-    <t>The Ratio datatype should only be used to express a relationship of two numbers if the relationship cannot be suitably expressed using a Quantity and a common unit.  Where the denominator value is known to be fixed to "1", Quantity should be used instead of Ratio.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-rat-1:Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.exists() and denominator.exists()) or (numerator.empty() and denominator.empty() and extension.exists())}</t>
-  </si>
-  <si>
-    <t>RTO</t>
-  </si>
-  <si>
     <t>Dosage.doseAndRate.rate[x]:rateRange</t>
   </si>
   <si>
@@ -1490,22 +1468,6 @@
 </t>
   </si>
   <si>
-    <t>範囲指定された時間の上限下限</t>
-  </si>
-  <si>
-    <t>時間の上限量、下限量の範囲を持っている。単位指定された数量を割り当てている。Low,Highの値は時間の単位当てはめる。</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-rng-2:If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
-  </si>
-  <si>
-    <t>IVL&lt;QTY[not(type="TS")]&gt; [lowClosed="true" and highClosed="true"]or URG&lt;QTY[not(type="TS")]&gt;</t>
-  </si>
-  <si>
-    <t>NR and also possibly SN (but see also quantity)</t>
-  </si>
-  <si>
     <t>Dosage.doseAndRate.rate[x]:rateQuantity</t>
   </si>
   <si>
@@ -1519,9 +1481,6 @@
     <t>投与速度(量/時間)を指定する</t>
   </si>
   <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
     <t>Dosage.maxDosePerPeriod</t>
   </si>
   <si>
@@ -1532,19 +1491,31 @@
     <t>単位時間当たりの投薬量の上限</t>
   </si>
   <si>
+    <t>This is intended for use as an adjunct to the dosage when there is an upper cap.  For example "2 tablets every 4 hours to a maximum of 8/day".</t>
+  </si>
+  <si>
     <t>The maximum total quantity of a therapeutic substance that may be administered to a subject over the period of time.  For example, 1000mg in 24 hours.</t>
   </si>
   <si>
+    <t>.maxDoseQuantity</t>
+  </si>
+  <si>
+    <t>RXO-23, RXE-19</t>
+  </si>
+  <si>
     <t>Dosage.maxDosePerAdministration</t>
   </si>
   <si>
     <t>1回あたりの投薬量の上限</t>
   </si>
   <si>
-    <t>薬剤に関する簡易的な数量と単位を定めている。ValueおよびCodeを必須とし、comparatorは記述不可。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
+    <t>This is intended for use as an adjunct to the dosage when there is an upper cap.  For example, a body surface area related dose with a maximum amount, such as 1.5 mg/m2 (maximum 2 mg) IV over 5 – 10 minutes would have doseQuantity of 1.5 mg/m2 and maxDosePerAdministration of 2 mg.</t>
   </si>
   <si>
     <t>The maximum total quantity of a therapeutic substance that may be administered to a subject per administration.</t>
+  </si>
+  <si>
+    <t>not supported</t>
   </si>
   <si>
     <t>Dosage.maxDosePerLifetime</t>
@@ -3122,7 +3093,7 @@
         <v>76</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K12" t="s" s="2">
         <v>148</v>
@@ -3131,13 +3102,13 @@
         <v>149</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -3201,18 +3172,18 @@
         <v>81</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>118</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3315,10 +3286,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3423,10 +3394,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3533,10 +3504,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3559,17 +3530,17 @@
         <v>113</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -3618,7 +3589,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3633,7 +3604,7 @@
         <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3641,10 +3612,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3667,17 +3638,17 @@
         <v>113</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3726,7 +3697,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3738,10 +3709,10 @@
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3749,10 +3720,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3855,10 +3826,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3963,10 +3934,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3989,13 +3960,13 @@
         <v>113</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4034,7 +4005,7 @@
         <v>76</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
@@ -4044,7 +4015,7 @@
         <v>98</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4059,7 +4030,7 @@
         <v>81</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>76</v>
@@ -4067,13 +4038,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>76</v>
@@ -4095,13 +4066,13 @@
         <v>113</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4152,7 +4123,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4167,7 +4138,7 @@
         <v>81</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
@@ -4175,10 +4146,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4281,10 +4252,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4389,10 +4360,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4415,19 +4386,19 @@
         <v>113</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4476,7 +4447,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4491,18 +4462,18 @@
         <v>81</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4525,23 +4496,23 @@
         <v>113</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q25" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="R25" t="s" s="2">
         <v>76</v>
@@ -4562,11 +4533,11 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>76</v>
@@ -4584,7 +4555,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4599,18 +4570,18 @@
         <v>81</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4636,21 +4607,21 @@
         <v>128</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>76</v>
@@ -4692,7 +4663,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4707,18 +4678,18 @@
         <v>81</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4741,24 +4712,24 @@
         <v>113</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>76</v>
@@ -4800,7 +4771,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4809,24 +4780,24 @@
         <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4849,26 +4820,26 @@
         <v>113</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>76</v>
@@ -4910,7 +4881,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4925,18 +4896,18 @@
         <v>81</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4959,19 +4930,19 @@
         <v>113</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>76</v>
@@ -5020,7 +4991,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5035,7 +5006,7 @@
         <v>81</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
@@ -5043,10 +5014,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5069,16 +5040,16 @@
         <v>113</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5128,7 +5099,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5143,7 +5114,7 @@
         <v>81</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
@@ -5151,10 +5122,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5177,19 +5148,19 @@
         <v>113</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5238,7 +5209,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5253,7 +5224,7 @@
         <v>81</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
@@ -5261,10 +5232,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5287,19 +5258,19 @@
         <v>113</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5348,7 +5319,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5363,7 +5334,7 @@
         <v>81</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>76</v>
@@ -5371,10 +5342,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5397,13 +5368,13 @@
         <v>113</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>146</v>
@@ -5432,11 +5403,11 @@
         <v>76</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>76</v>
@@ -5454,7 +5425,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5469,7 +5440,7 @@
         <v>81</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
@@ -5477,10 +5448,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5503,23 +5474,23 @@
         <v>113</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R34" t="s" s="2">
         <v>76</v>
@@ -5564,7 +5535,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5579,7 +5550,7 @@
         <v>81</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5587,10 +5558,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5613,16 +5584,16 @@
         <v>113</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5672,7 +5643,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5687,7 +5658,7 @@
         <v>81</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
@@ -5695,10 +5666,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5721,16 +5692,16 @@
         <v>113</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5780,7 +5751,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5795,7 +5766,7 @@
         <v>81</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
@@ -5803,10 +5774,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5829,16 +5800,16 @@
         <v>113</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5888,7 +5859,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5903,7 +5874,7 @@
         <v>81</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -5911,10 +5882,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5937,13 +5908,13 @@
         <v>113</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>146</v>
@@ -5972,11 +5943,11 @@
         <v>76</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>76</v>
@@ -5994,7 +5965,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6009,7 +5980,7 @@
         <v>81</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -6017,10 +5988,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6043,16 +6014,16 @@
         <v>113</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6078,11 +6049,11 @@
         <v>76</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>76</v>
@@ -6100,7 +6071,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6123,10 +6094,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6149,16 +6120,16 @@
         <v>113</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6208,7 +6179,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6231,10 +6202,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6257,19 +6228,19 @@
         <v>113</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
@@ -6294,11 +6265,11 @@
         <v>76</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>76</v>
@@ -6316,7 +6287,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6331,7 +6302,7 @@
         <v>81</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>76</v>
@@ -6339,10 +6310,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6365,16 +6336,16 @@
         <v>113</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6424,7 +6395,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6439,7 +6410,7 @@
         <v>81</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
@@ -6447,10 +6418,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6476,13 +6447,13 @@
         <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6512,7 +6483,7 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>76</v>
@@ -6530,7 +6501,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6545,7 +6516,7 @@
         <v>81</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
@@ -6553,10 +6524,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6579,16 +6550,16 @@
         <v>113</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6638,7 +6609,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6653,18 +6624,18 @@
         <v>81</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6690,16 +6661,16 @@
         <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>76</v>
@@ -6728,7 +6699,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>76</v>
@@ -6746,7 +6717,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6761,18 +6732,18 @@
         <v>81</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6798,16 +6769,16 @@
         <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6836,7 +6807,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>76</v>
@@ -6854,7 +6825,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6869,18 +6840,18 @@
         <v>81</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6906,16 +6877,16 @@
         <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -6940,11 +6911,11 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>76</v>
@@ -6962,7 +6933,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6977,18 +6948,18 @@
         <v>81</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7091,10 +7062,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7199,10 +7170,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7225,19 +7196,19 @@
         <v>113</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>76</v>
@@ -7274,7 +7245,7 @@
         <v>76</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -7284,7 +7255,7 @@
         <v>98</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7299,21 +7270,21 @@
         <v>81</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>76</v>
@@ -7335,19 +7306,19 @@
         <v>113</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>76</v>
@@ -7376,7 +7347,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>76</v>
@@ -7394,7 +7365,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7409,18 +7380,18 @@
         <v>81</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7523,10 +7494,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7631,10 +7602,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7657,26 +7628,26 @@
         <v>113</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>76</v>
@@ -7718,7 +7689,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7733,18 +7704,18 @@
         <v>81</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7770,13 +7741,13 @@
         <v>128</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7826,7 +7797,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7841,18 +7812,18 @@
         <v>81</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7875,17 +7846,17 @@
         <v>113</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -7934,7 +7905,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7949,18 +7920,18 @@
         <v>81</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7986,14 +7957,14 @@
         <v>128</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -8042,7 +8013,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8057,18 +8028,18 @@
         <v>81</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8091,19 +8062,19 @@
         <v>113</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -8152,7 +8123,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8167,21 +8138,21 @@
         <v>81</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>76</v>
@@ -8203,19 +8174,19 @@
         <v>113</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8244,7 +8215,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>76</v>
@@ -8262,7 +8233,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8277,18 +8248,18 @@
         <v>81</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8391,10 +8362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8499,10 +8470,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8525,26 +8496,26 @@
         <v>113</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>76</v>
@@ -8586,7 +8557,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8601,18 +8572,18 @@
         <v>81</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8638,13 +8609,13 @@
         <v>128</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8694,7 +8665,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -8709,18 +8680,18 @@
         <v>81</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8743,17 +8714,17 @@
         <v>113</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>76</v>
@@ -8802,7 +8773,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8817,18 +8788,18 @@
         <v>81</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8854,14 +8825,14 @@
         <v>128</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
@@ -8910,7 +8881,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -8925,18 +8896,18 @@
         <v>81</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8959,19 +8930,19 @@
         <v>113</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -9020,7 +8991,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9035,18 +9006,18 @@
         <v>81</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9130,7 +9101,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9145,18 +9116,18 @@
         <v>81</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9179,13 +9150,13 @@
         <v>113</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9236,7 +9207,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9248,21 +9219,21 @@
         <v>76</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9365,10 +9336,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9473,10 +9444,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9502,16 +9473,16 @@
         <v>135</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>76</v>
@@ -9540,7 +9511,7 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>76</v>
@@ -9558,7 +9529,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9576,15 +9547,15 @@
         <v>76</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9604,22 +9575,22 @@
         <v>76</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>76</v>
@@ -9668,7 +9639,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9677,24 +9648,24 @@
         <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>453</v>
+        <v>76</v>
       </c>
       <c r="AJ72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>456</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9717,19 +9688,19 @@
         <v>113</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>76</v>
@@ -9766,17 +9737,17 @@
         <v>76</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AC73" s="2"/>
       <c r="AD73" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -9791,21 +9762,21 @@
         <v>81</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>76</v>
@@ -9824,22 +9795,22 @@
         <v>76</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>76</v>
@@ -9888,7 +9859,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -9897,27 +9868,27 @@
         <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>453</v>
+        <v>76</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>471</v>
+        <v>81</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>118</v>
+        <v>463</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>76</v>
@@ -9936,22 +9907,22 @@
         <v>76</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>76</v>
@@ -10000,7 +9971,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10009,27 +9980,27 @@
         <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>453</v>
+        <v>76</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>478</v>
+        <v>81</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>480</v>
+        <v>463</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>76</v>
@@ -10048,22 +10019,22 @@
         <v>76</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>485</v>
+        <v>459</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>76</v>
@@ -10112,7 +10083,7 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -10121,24 +10092,24 @@
         <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>453</v>
+        <v>76</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>454</v>
+        <v>81</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10158,22 +10129,22 @@
         <v>76</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>76</v>
@@ -10222,7 +10193,7 @@
         <v>76</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10231,24 +10202,24 @@
         <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>453</v>
+        <v>76</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>471</v>
+        <v>81</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>118</v>
+        <v>480</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10268,22 +10239,22 @@
         <v>76</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>76</v>
@@ -10332,7 +10303,7 @@
         <v>76</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10341,24 +10312,24 @@
         <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>453</v>
+        <v>76</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>454</v>
+        <v>81</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>456</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10378,22 +10349,20 @@
         <v>76</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>76</v>
@@ -10442,7 +10411,7 @@
         <v>76</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -10451,16 +10420,16 @@
         <v>84</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>453</v>
+        <v>76</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>454</v>
+        <v>81</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>456</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationdosage.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationdosage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -1098,7 +1098,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.3.0</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -1196,7 +1196,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.30</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodBasicUsage</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1316,7 +1316,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コード</t>
   </si>
   <si>
-    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードurn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
@@ -1331,7 +1331,7 @@
     <t>Dosage.method.coding:unitDigit2.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodDetailUsage</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit2.version</t>
@@ -1422,7 +1422,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity}</t>
+RangeQuantity {SimpleQuantity|4.3.0}</t>
   </si>
   <si>
     <t>薬剤の投与量速度</t>
@@ -1831,17 +1831,17 @@
   <dimension ref="A1:AL79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="57.37109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.0625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.734375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="21.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.18359375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="36.05859375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.48828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="96.27734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="82.5390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1850,24 +1850,24 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="77.19140625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="128.11328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="45.6171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="109.8359375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationdosage.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationdosage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationdosage.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationdosage.xlsx
@@ -259,7 +259,7 @@
     <t>薬の服用方法・服用した方法、または服用すべき方法</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -276,10 +276,10 @@
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -299,13 +299,13 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -321,8 +321,8 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Dosage.extension:periodOfUse</t>
@@ -367,14 +367,15 @@
     <t>Y</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -477,16 +478,16 @@
 </t>
   </si>
   <si>
-    <t>When medication should be administered</t>
-  </si>
-  <si>
-    <t>When medication should be administered.</t>
-  </si>
-  <si>
-    <t>This attribute might not always be populated while the Dosage.text is expected to be populated.  If both are populated, then the Dosage.text should reflect the content of the Dosage.timing.</t>
-  </si>
-  <si>
-    <t>The timing schedule for giving the medication to the patient. This  data type allows many different expressions. For example: "Every 8 hours"; "Three times a day"; "1/2 an hour before breakfast for 10 days from 23-Dec 2011:"; "15 Oct 2013, 17 Oct 2013 and 1 Nov 2013".  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
+    <t>薬を投与する必要がある場合 / When medication should be administered</t>
+  </si>
+  <si>
+    <t>薬を投与する必要がある場合。 / When medication should be administered.</t>
+  </si>
+  <si>
+    <t>この属性は、Dosage.Textが入力されると予想される間、常に埋め込まれるとは限りません。両方が入力されている場合、Dosage.textはDosage.timingの内容を反映する必要があります。 / This attribute might not always be populated while the Dosage.text is expected to be populated.  If both are populated, then the Dosage.text should reflect the content of the Dosage.timing.</t>
+  </si>
+  <si>
+    <t>患者への薬剤投与のタイミングスケジュール。このデータ型は多くの異なる表現を許可します。例えば：「8時間ごと」、「1日3回」、「2011年12月23日から10日間、朝食の30分前」、「2013年10月15日、2013年10月17日、2013年11月1日」。場合によっては、速度が総量/期間として表現される場合、期間を暗示することがあります（例：500mL/2時間は2時間の期間を暗示）。ただし、速度が期間を暗示しない場合（例：250mL/時間）、timing.repeat.durationが注入期間を伝えるために必要です。 / The timing schedule for giving the medication to the patient. This  data type allows many different expressions. For example: "Every 8 hours"; "Three times a day"; "1/2 an hour before breakfast for 10 days from 23-Dec 2011:"; "15 Oct 2013, 17 Oct 2013 and 1 Nov 2013".  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
   </si>
   <si>
     <t>.effectiveTime</t>
@@ -514,7 +515,7 @@
     <t>服用タイミングを具体的な日時で指定する場合に使用する</t>
   </si>
   <si>
-    <t>In a Medication Administration Record, for instance, you need to take a general specification, and turn it into a precise specification.</t>
+    <t>たとえば、投薬投与の記録では、一般的な仕様を取得し、それを正確な仕様に変える必要があります。 / In a Medication Administration Record, for instance, you need to take a general specification, and turn it into a precise specification.</t>
   </si>
   <si>
     <t>Timing.event</t>
@@ -542,8 +543,8 @@
     <t>Timing.repeat</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-tim-1:if there's a duration, there needs to be duration units {duration.empty() or durationUnit.exists()}tim-2:if there's a period, there needs to be period units {period.empty() or periodUnit.exists()}tim-4:duration SHALL be a non-negative value {duration.exists() implies duration &gt;= 0}tim-5:period SHALL be a non-negative value {period.exists() implies period &gt;= 0}tim-6:If there's a periodMax, there must be a period {periodMax.empty() or period.exists()}tim-7:If there's a durationMax, there must be a duration {durationMax.empty() or duration.exists()}tim-8:If there's a countMax, there must be a count {countMax.empty() or count.exists()}tim-9:If there's an offset, there must be a when (and not C, CM, CD, CV) {offset.empty() or (when.exists() and ((when in ('C' | 'CM' | 'CD' | 'CV')).not()))}tim-10:If there's a timeOfDay, there cannot be a when, or vice versa {timeOfDay.empty() or when.empty()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+tim-1:期間がある場合は、期間単位が必要です / if there's a duration, there needs to be duration units {duration.empty() or durationUnit.exists()}tim-2:期間がある場合、期間単位が必要です / if there's a period, there needs to be period units {period.empty() or periodUnit.exists()}tim-4:期間は非陰性価値です / duration SHALL be a non-negative value {duration.exists() implies duration &gt;= 0}tim-5:期間は非陰性の価値です / period SHALL be a non-negative value {period.exists() implies period &gt;= 0}tim-6:期間がある場合、期間がなければなりません / If there's a periodMax, there must be a period {periodMax.empty() or period.exists()}tim-7:Hurtermaxがある場合、期間がなければなりません / If there's a durationMax, there must be a duration {durationMax.empty() or duration.exists()}tim-8:countmaxがある場合、カウントが必要です / If there's a countMax, there must be a count {countMax.empty() or count.exists()}tim-9:オフセットがある場合、c、cm、cd、cvではなく（c、cvではない）存在する必要があります。 / If there's an offset, there must be a when (and not C, CM, CD, CV) {offset.empty() or (when.exists() and ((when in ('C' | 'CM' | 'CD' | 'CV')).not()))}tim-10:時間がある場合、いつ、またはその逆もありません / If there's a timeOfDay, there cannot be a when, or vice versa {timeOfDay.empty() or when.empty()}</t>
   </si>
   <si>
     <t>Implies PIVL or EIVL</t>
@@ -613,10 +614,10 @@
     <t>投薬日数</t>
   </si>
   <si>
-    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
-  </si>
-  <si>
-    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+    <t>値の暗黙の精度は常に尊重されるべきです。金銭的価値には、精度を処理するための独自のルールがあります（標準的な会計の教科書を参照）。 / The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>精度は、測定のほとんどすべての場合に暗黙的に処理されます。 / Precision is handled implicitly in almost all cases of measurement.</t>
   </si>
   <si>
     <t>Quantity.value</t>
@@ -638,16 +639,16 @@
 </t>
   </si>
   <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
-  </si>
-  <si>
-    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
-  </si>
-  <si>
-    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
-  </si>
-  <si>
-    <t>If there is no comparator, then there is no modification of the value</t>
+    <t>&lt;|&lt;= |&gt; = |&gt;  - 値の比較方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
+    <t>値をどのように理解し、表現する必要があるか - 測定の問題により実際の値が記載されている値よりも大きいか小さいかどうか。例えばコンパレータが「&lt;」の場合、実際の値は&lt;stated値です。 / How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
+  </si>
+  <si>
+    <t>測定方法の制限があるため、値が&lt;5ug/Lまたは&gt; 400mg/Lの測定値を処理するためのフレームワークが必要です。 / Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>コンパレータがない場合、値の変更はありません / If there is no comparator, then there is no modification of the value</t>
   </si>
   <si>
     <t>required</t>
@@ -677,7 +678,7 @@
     <t>投薬日数の単位文字列。日で固定される</t>
   </si>
   <si>
-    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+    <t>測定単位には多くの表現があり、多くのコンテキストでは、特定の表現が固定され、必要です。すなわちマイクログラム用MCG。 / There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
   </si>
   <si>
     <t>日</t>
@@ -708,7 +709,7 @@
     <t>単位コード UCUMを識別するURI。固定値。</t>
   </si>
   <si>
-    <t>Need to know the system that defines the coded form of the unit.</t>
+    <t>ユニットのコード化された形式を定義するシステムを知る必要があります。 / Need to know the system that defines the coded form of the unit.</t>
   </si>
   <si>
     <t>http://unitsofmeasure.org</t>
@@ -736,10 +737,10 @@
     <t>単位コードUCUMにおける投与日数の単位。dで固定される。</t>
   </si>
   <si>
-    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
-  </si>
-  <si>
-    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+    <t>優先システムはUCUMですが、独自の単位にはSNOMED-CT、または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>すべてのフォームに固定されたユニットの計算可能な形式が必要です。UCUMはこれを数量で提供しますが、Snomed CTは多くの関心のある単位を提供します。 / Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
   </si>
   <si>
     <t>d</t>
@@ -767,7 +768,7 @@
     <t>回数に上限、下限の範囲がある場合は、このcountで示される回数が起きるまでは、エレメントは範囲の中にあると解釈されるべきである。</t>
   </si>
   <si>
-    <t>Repetitions may be limited by end time or total occurrences.</t>
+    <t>繰り返しは、終了時間または合計発生によって制限される場合があります。 / Repetitions may be limited by end time or total occurrences.</t>
   </si>
   <si>
     <t>Timing.repeat.count</t>
@@ -827,7 +828,7 @@
     <t>Dosage.timing.repeat.durationUnit</t>
   </si>
   <si>
-    <t>s | min | h | d | wk | mo | a - unit of time (UCUM)</t>
+    <t>s |min |h |d |wk |mo |A-時間単位（ucum） / s | min | h | d | wk | mo | a - unit of time (UCUM)</t>
   </si>
   <si>
     <t>UCUM単位で表される継続時間についての単位。</t>
@@ -854,7 +855,7 @@
     <t>32ビットの数値。もし、値がそれを上回るようであればdecimalを使用する。</t>
   </si>
   <si>
-    <t>If no frequency is stated, the assumption is that the event occurs once per period, but systems SHOULD always be specific about this</t>
+    <t>頻度が記載されていない場合、イベントは期間ごとに1回発生するという仮定ですが、システムは常にこれについて具体的でなければなりません / If no frequency is stated, the assumption is that the event occurs once per period, but systems SHOULD always be specific about this</t>
   </si>
   <si>
     <t>Timing.repeat.frequency</t>
@@ -914,7 +915,7 @@
     <t>Dosage.timing.repeat.dayOfWeek</t>
   </si>
   <si>
-    <t>mon | tue | wed | thu | fri | sat | sun</t>
+    <t>月|火|水|木|金|土|太陽 / mon | tue | wed | thu | fri | sat | sun</t>
   </si>
   <si>
     <t>期間として1週間以上が指定されていれば、指定された曜日のみで投与が行われる。</t>
@@ -994,7 +995,7 @@
     <t>Dosage.timing.code</t>
   </si>
   <si>
-    <t>BID | TID | QID | AM | PM | QD | QOD | +</t>
+    <t>入札|TID |QID |AM |PM |QD |qod |+ / BID | TID | QID | AM | PM | QD | QOD | +</t>
   </si>
   <si>
     <t>スケジュール上のタイミングを表すコード（あるいはcode.text内のテキスト）。BID(1日2回)のようなコードはどこにでもあるが、多くの医療機関は付加的なコードを定義している。もし、コードが示されていれば、構造化されたタイミングで完全に示されたデータであると解釈され、コードまたはTimingを解釈するためのデータであると解釈される。しかし、例外的に.repeat.bounds（コードは含まれない)はコードを上書きして適用される。</t>
@@ -1027,7 +1028,7 @@
 Medication(薬剤)が必要なときに指定された量とスケジュールのみで投薬するか（Booleanで選択される）、投薬する前提条件はTiming.Code(CodeableConcept)を示している。</t>
   </si>
   <si>
-    <t>Can express "as needed" without a reason by setting the Boolean = True.  In this case the CodeableConcept is not populated.  Or you can express "as needed" with a reason by including the CodeableConcept.  In this case the Boolean is assumed to be True.  If you set the Boolean to False, then the dose is given according to the schedule and is not "prn" or "as needed".</t>
+    <t>boolean = trueを設定することにより、理由なしに「必要に応じて」表現できます。この場合、codeableconceptは存在しません。または、Codeableconceptを含めることにより、「必要に応じて」理由で「必要に応じて」表現することができます。この場合、ブール値は真であると想定されています。ブール値をfalseに設定すると、用量はスケジュールに従って与えられ、「PRN」または「必要に応じて」ではありません。 / Can express "as needed" without a reason by setting the Boolean = True.  In this case the CodeableConcept is not populated.  Or you can express "as needed" with a reason by including the CodeableConcept.  In this case the Boolean is assumed to be True.  If you set the Boolean to False, then the dose is given according to the schedule and is not "prn" or "as needed".</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=PRCN].target[classCode=OBS, moodCode=EVN, code="as needed"].value=boolean or codable concept</t>
@@ -1049,7 +1050,7 @@
 【JP Core仕様】JAMI外用部位３桁コードを使用することが望ましいが、ローカルコードも使用可能。</t>
   </si>
   <si>
-    <t>A coded specification of the anatomic site where the medication first enters the body.</t>
+    <t>薬が最初に体に入る解剖学的部位のコード化された仕様。 / A coded specification of the anatomic site where the medication first enters the body.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
@@ -1071,7 +1072,7 @@
 【JP Core仕様】HL7表0162をベースにした投与経路コードを使用することが望ましいが、ローカルコードも使用可能。</t>
   </si>
   <si>
-    <t>A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
+    <t>患者の体への、または患者の体内への治療剤の投与のルートまたは生理学的経路を指定するコード。 / A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS</t>
@@ -1120,16 +1121,16 @@
 </t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
@@ -1184,16 +1185,16 @@
     <t>Dosage.method.coding.system</t>
   </si>
   <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
     <t>http://jami.jp/CodeSystem/MedicationMethodBasicUsage</t>
@@ -1214,13 +1215,13 @@
     <t>Dosage.method.coding.version</t>
   </si>
   <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
   </si>
   <si>
     <t>Coding.version</t>
@@ -1238,13 +1239,13 @@
     <t>Dosage.method.coding.code</t>
   </si>
   <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
+    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -1262,13 +1263,13 @@
     <t>Dosage.method.coding.display</t>
   </si>
   <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+    <t>システムによって定義された表現 / Representation defined by the system</t>
+  </si>
+  <si>
+    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
     <t>Coding.display</t>
@@ -1286,16 +1287,16 @@
     <t>Dosage.method.coding.userSelected</t>
   </si>
   <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
   </si>
   <si>
     <t>Coding.userSelected</t>
@@ -1367,7 +1368,7 @@
     <t>薬剤が投与される量</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -1412,7 +1413,7 @@
 【JP Core仕様】1回の投与量を指定する。単位は医薬品単位略号を使用することが望ましい。</t>
   </si>
   <si>
-    <t>The amount of therapeutic or other substance given at one administration event.</t>
+    <t>1つの投与イベントで与えられた治療またはその他の物質の量。 / The amount of therapeutic or other substance given at one administration event.</t>
   </si>
   <si>
     <t>RXO-2, RXE-3</t>
@@ -1431,12 +1432,14 @@
     <t>薬剤が投与される量の速度</t>
   </si>
   <si>
-    <t>It is possible to supply both a rate and a doseQuantity to provide full details about how the medication is to be administered and supplied. If the rate is intended to change over time, depending on local rules/regulations, each change should be captured as a new version of the MedicationRequest with an updated rate, or captured with a new MedicationRequest with the new rate.+    <t>レートとデスケーティティの両方を供給して、薬の投与と供給の方法についての詳細を提供することができます。レートが時間の経過とともに変化することを目的としている場合、ローカルのルール/規制に応じて、各変更は、更新されたレートのある薬物療法の新しいバージョンとしてキャプチャするか、新しいレートで新しい薬物採取でキャプチャされる必要があります。++レート（100 ml/hour）を使用して、時間の経過とともにレートを指定することができます。RateQuantityアプローチでは、時間が分母として指定されている特定の比率ではなく、ML/時間が含まれているUCUMグラマーを解析する機能をシステムに持つ必要があります。2時間にわたって500mlなどのレートが指定されている場合、250 mg/時のレートの量を使用して指定するよりも、定量的に正しい場合があります。 / It is possible to supply both a rate and a doseQuantity to provide full details about how the medication is to be administered and supplied. If the rate is intended to change over time, depending on local rules/regulations, each change should be captured as a new version of the MedicationRequest with an updated rate, or captured with a new MedicationRequest with the new rate.  It is possible to specify a rate over time (for example, 100 ml/hour) using either the rateRatio and rateQuantity.  The rateQuantity approach requires systems to have the capability to parse UCUM grammer where ml/hour is included rather than a specific ratio where the time is specified as the denominator.  Where a rate such as 500ml over 2 hours is specified, the use of rateRatio may be more semantically correct than specifying using a rateQuantity of 250 mg/hour.</t>
   </si>
   <si>
-    <t>Identifies the speed with which the medication was or will be introduced into the patient. Typically the rate for an infusion e.g. 100 ml per 1 hour or 100 ml/hr.  May also be expressed as a rate per unit of time e.g. 500 ml per 2 hours.   Other examples: 200 mcg/min or 200 mcg/1 minute; 1 liter/8 hours.  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
+    <t>薬剤が患者に投与された速度または投与される速度を識別します。通常、輸液の場合は1時間あたり100mlまたは100ml/hrなどの速度です。時間の単位あたりの速度として表現することもできます（例：2時間あたり500ml）。その他の例：200 mcg/分または200 mcg/1分、1リットル/8時間。場合によっては、速度が総量/期間として表現される場合、期間を暗示することがあります（例：500mL/2時間は2時間の期間を暗示）。ただし、速度が期間を暗示しない場合（例：250mL/時間）、timing.repeat.durationが注入期間を伝えるために必要です。 / Identifies the speed with which the medication was or will be introduced into the patient. Typically the rate for an infusion e.g. 100 ml per 1 hour or 100 ml/hr.  May also be expressed as a rate per unit of time e.g. 500 ml per 2 hours.   Other examples: 200 mcg/min or 200 mcg/1 minute; 1 liter/8 hours.  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
   </si>
   <si>
     <t>closed</t>
@@ -1491,10 +1494,10 @@
     <t>単位時間当たりの投薬量の上限</t>
   </si>
   <si>
-    <t>This is intended for use as an adjunct to the dosage when there is an upper cap.  For example "2 tablets every 4 hours to a maximum of 8/day".</t>
-  </si>
-  <si>
-    <t>The maximum total quantity of a therapeutic substance that may be administered to a subject over the period of time.  For example, 1000mg in 24 hours.</t>
+    <t>これは、上限があるときに投与量の補助として使用することを目的としています。たとえば、「4時間ごとに最大8時間あたり2錠」。 / This is intended for use as an adjunct to the dosage when there is an upper cap.  For example "2 tablets every 4 hours to a maximum of 8/day".</t>
+  </si>
+  <si>
+    <t>期間にわたって被験者に投与される可能性のある治療物質の最大総量。たとえば、24時間で1000mg。 / The maximum total quantity of a therapeutic substance that may be administered to a subject over the period of time.  For example, 1000mg in 24 hours.</t>
   </si>
   <si>
     <t>.maxDoseQuantity</t>
@@ -1509,10 +1512,10 @@
     <t>1回あたりの投薬量の上限</t>
   </si>
   <si>
-    <t>This is intended for use as an adjunct to the dosage when there is an upper cap.  For example, a body surface area related dose with a maximum amount, such as 1.5 mg/m2 (maximum 2 mg) IV over 5 – 10 minutes would have doseQuantity of 1.5 mg/m2 and maxDosePerAdministration of 2 mg.</t>
-  </si>
-  <si>
-    <t>The maximum total quantity of a therapeutic substance that may be administered to a subject per administration.</t>
+    <t>これは、上限があるときに投与量の補助として使用することを目的としています。たとえば、5〜10分間で1.5 mg/m2（最大2 mg）IVなどの最大量の体積領域に関連する用量に関連する用量は、1.5 mg/m2、最大2 mgのDosequantityになります。 / This is intended for use as an adjunct to the dosage when there is an upper cap.  For example, a body surface area related dose with a maximum amount, such as 1.5 mg/m2 (maximum 2 mg) IV over 5 – 10 minutes would have doseQuantity of 1.5 mg/m2 and maxDosePerAdministration of 2 mg.</t>
+  </si>
+  <si>
+    <t>投与ごとの被験者に投与される可能性のある治療物質の最大総量。 / The maximum total quantity of a therapeutic substance that may be administered to a subject per administration.</t>
   </si>
   <si>
     <t>not supported</t>
@@ -1524,7 +1527,7 @@
     <t>生涯の投薬量の上限</t>
   </si>
   <si>
-    <t>The maximum total quantity of a therapeutic substance that may be administered per lifetime of the subject.</t>
+    <t>被験者の寿命ごとに投与される可能性のある治療物質の最大総量。 / The maximum total quantity of a therapeutic substance that may be administered per lifetime of the subject.</t>
   </si>
 </sst>
 </file>
